--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.76216512574356</v>
+        <v>10.19885183293333</v>
       </c>
       <c r="D2" t="n">
-        <v>29.6958257553569</v>
+        <v>4.825571685245496</v>
       </c>
       <c r="E2" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F2" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.23763223594906</v>
+        <v>8.651115238341724</v>
       </c>
       <c r="D3" t="n">
-        <v>52.4882877835165</v>
+        <v>8.529346764821433</v>
       </c>
       <c r="E3" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F3" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.326149899741</v>
+        <v>3.627999358707913</v>
       </c>
       <c r="D4" t="n">
-        <v>28.63093421998206</v>
+        <v>4.652526810747085</v>
       </c>
       <c r="E4" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F4" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.25213460966256</v>
+        <v>1.178471874070166</v>
       </c>
       <c r="D5" t="n">
-        <v>9.11872783722832</v>
+        <v>1.481793273549602</v>
       </c>
       <c r="E5" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F5" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.07544350928313</v>
+        <v>4.562259570258509</v>
       </c>
       <c r="D6" t="n">
-        <v>30.38180689756862</v>
+        <v>4.937043620854902</v>
       </c>
       <c r="E6" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F6" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.90840162207344</v>
+        <v>8.110115263586934</v>
       </c>
       <c r="D7" t="n">
-        <v>52.75261262530543</v>
+        <v>8.572299551612133</v>
       </c>
       <c r="E7" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F7" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.9358568280432</v>
+        <v>2.91457673455702</v>
       </c>
       <c r="D8" t="n">
-        <v>13.86781678410657</v>
+        <v>2.253520227417317</v>
       </c>
       <c r="E8" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F8" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.70951036459988</v>
+        <v>4.827795434247481</v>
       </c>
       <c r="D9" t="n">
-        <v>23.87619272615382</v>
+        <v>3.879881317999996</v>
       </c>
       <c r="E9" t="n">
-        <v>18.07498193982133</v>
+        <v>2.937184565220967</v>
       </c>
       <c r="F9" t="n">
-        <v>14.82906995873629</v>
+        <v>2.409723868294647</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
